--- a/data/gravel/Awson Gravel GT 2025.xlsx
+++ b/data/gravel/Awson Gravel GT 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E29C666-0D54-A545-9D0C-667AE2D4E6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C3B80F-6F69-C448-AE7D-A7B0FDBCC2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3400" yWindow="740" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,9 +335,6 @@
     <t>integrated</t>
   </si>
   <si>
-    <t>spec'd tire size</t>
-  </si>
-  <si>
     <t>https://awson-swiss.com/wp-content/uploads/2024/02/20231204_AWSON4009_HR-Kopie-1.jpg</t>
   </si>
   <si>
@@ -348,6 +345,9 @@
   </si>
   <si>
     <t>a8:g32</t>
+  </si>
+  <si>
+    <t>instagram message</t>
   </si>
 </sst>
 </file>
@@ -754,12 +754,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
@@ -767,7 +767,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H7" s="1"/>
     </row>
@@ -776,7 +776,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="4">
         <v>49</v>
@@ -794,7 +794,7 @@
         <v>58</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>85</v>
@@ -1467,19 +1467,19 @@
         <v>26</v>
       </c>
       <c r="C30">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D30">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E30">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F30">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G30">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -1550,10 +1550,10 @@
         <v>34</v>
       </c>
       <c r="B41">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">

--- a/data/gravel/Awson Gravel GT 2025.xlsx
+++ b/data/gravel/Awson Gravel GT 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C3B80F-6F69-C448-AE7D-A7B0FDBCC2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAF6D5A-71C2-534C-AA4D-419EA33BFD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3400" yWindow="740" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -287,9 +287,6 @@
     <t>Awson</t>
   </si>
   <si>
-    <t>Gravel ART</t>
-  </si>
-  <si>
     <t>ST</t>
   </si>
   <si>
@@ -348,6 +345,9 @@
   </si>
   <si>
     <t>instagram message</t>
+  </si>
+  <si>
+    <t>Gravel GT</t>
   </si>
 </sst>
 </file>
@@ -730,7 +730,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -754,12 +754,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
@@ -767,7 +767,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H7" s="1"/>
     </row>
@@ -776,7 +776,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="4">
         <v>49</v>
@@ -794,43 +794,43 @@
         <v>58</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="L8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="M8" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="N8" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="O8" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="Q8" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="Q8" s="5" t="s">
+      <c r="R8" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="S8" s="5" t="s">
+      <c r="T8" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="T8" s="5" t="s">
+      <c r="U8" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
@@ -838,7 +838,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" s="4">
         <v>470</v>
@@ -901,7 +901,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4">
         <v>515</v>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" s="4">
         <v>105</v>
@@ -1027,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="4">
         <v>70.5</v>
@@ -1090,7 +1090,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="4">
         <v>74.5</v>
@@ -1153,7 +1153,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C14" s="4">
         <v>76</v>
@@ -1183,7 +1183,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C15" s="4">
         <v>435</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="16" spans="1:21" ht="21" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" s="4">
         <v>587</v>
@@ -1244,7 +1244,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" s="4">
         <v>50</v>
@@ -1275,7 +1275,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="4">
         <v>1010</v>
@@ -1306,7 +1306,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C19" s="4">
         <v>536</v>
@@ -1337,7 +1337,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C20" s="4">
         <v>366</v>
@@ -1553,7 +1553,7 @@
         <v>45</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -1683,7 +1683,7 @@
         <v>51</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -1790,7 +1790,7 @@
         <v>72</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
